--- a/sipii_caixa_20260601.xlsx
+++ b/sipii_caixa_20260601.xlsx
@@ -5676,62 +5676,58 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CAIXA FIC FIF BETA RF REF DI LP RESP LTDA</t>
+          <t>CAIXA SIGMA FUNCIONARIOS FIC FIF RF REF DI LP - RESP LTDA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>02/10/1995</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>30,23758400</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>0,048</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t>0,96</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>5,08</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>13,21</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>165,211</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>PF | TODOS</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/referenciados/fic-beta-ref-di-lp</t>
-        </is>
-      </c>
+          <t>PF</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>00.834.072/0001-34</t>
+          <t>66.034.762/0001-17</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5741,7 +5737,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5761,32 +5757,32 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_0056.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_8500.pdf</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_0056.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_8500.pdf</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_0056.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_8500.pdf</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_0056.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_8500.pdf</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_56.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_8500.pdf</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_56.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_8500.pdf</t>
         </is>
       </c>
     </row>
@@ -5798,58 +5794,62 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>CAIXA SIGMA FUNCIONARIOS FIC FIF RF REF DI LP - RESP LTDA</t>
+          <t>CAIXA FIC FIF BETA RF REF DI LP RESP LTDA</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>02/10/1995</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>30,23758400</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>0,048</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>0,96</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>5,08</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>13,21</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>165,211</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>PF</t>
-        </is>
-      </c>
-      <c r="K45" s="4" t="inlineStr"/>
+          <t>PF | TODOS</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/fundos-investimento/referenciados/fic-beta-ref-di-lp</t>
+        </is>
+      </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>66.034.762/0001-17</t>
+          <t>00.834.072/0001-34</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
@@ -5879,32 +5879,32 @@
       </c>
       <c r="S45" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_8500.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_0056.pdf</t>
         </is>
       </c>
       <c r="T45" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_8500.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_0056.pdf</t>
         </is>
       </c>
       <c r="U45" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_8500.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_0056.pdf</t>
         </is>
       </c>
       <c r="V45" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_8500.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_0056.pdf</t>
         </is>
       </c>
       <c r="W45" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_8500.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_56.pdf</t>
         </is>
       </c>
       <c r="X45" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_8500.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_56.pdf</t>
         </is>
       </c>
     </row>

--- a/sipii_caixa_20260601.xlsx
+++ b/sipii_caixa_20260601.xlsx
@@ -659,7 +659,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>407,706</t>
+          <t>402,851</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>6.783,321</t>
+          <t>6.646,794</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>876,296</t>
+          <t>886,956</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>11,649</t>
+          <t>11,550</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>120,046</t>
+          <t>119,002</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>97,403</t>
+          <t>96,504</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>586,164</t>
+          <t>581,391</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>61,836</t>
+          <t>61,339</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1.674,712</t>
+          <t>1.661,172</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>123,417</t>
+          <t>122,783</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,382</t>
+          <t>28,033</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>03.218.183/0001-04</t>
+          <t>03.191.874/0001-61</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>100000.0</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1873,32 +1873,32 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_0087.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_0046.pdf</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_0087.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_0046.pdf</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_0087.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_0046.pdf</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_87.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_46.pdf</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_87.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_46.pdf</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_87.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_46.pdf</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>40,715</t>
+          <t>40,384</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,881</t>
+          <t>64,363</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>79,838</t>
+          <t>79,084</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,956</t>
+          <t>27,719</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>1,659</t>
+          <t>1,646</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -2555,7 +2555,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>139,380</t>
+          <t>138,691</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>1.801,377</t>
+          <t>1.771,652</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="Q19" s="4" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2.192,556</t>
+          <t>2.175,893</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>13,227</t>
+          <t>13,106</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,747</t>
+          <t>66,269</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>957,410</t>
+          <t>948,894</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,11446441</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>-0,039</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>0,39</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>3,31</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>212,664</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3384,32 +3384,32 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,23544100</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>-0,001</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>1,22</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>5,48</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>14,65</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>71,169</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>175,484</t>
+          <t>173,953</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>40,304</t>
+          <t>39,867</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -3750,32 +3750,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,03539400</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>-0,001</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>5,59</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21,752</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3868,32 +3868,32 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,16411800</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>-0,001</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>1,39</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>4,83</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>13,88</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>66,448</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -3986,32 +3986,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,06921896</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>0,149</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>1,40</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>3,47</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>311,054</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       <c r="O31" s="4" t="inlineStr"/>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="Q31" s="4" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>861,613</t>
+          <t>851,672</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>3.249,946</t>
+          <t>3.222,999</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,281</t>
+          <t>21,029</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>3.114,091</t>
+          <t>3.090,447</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>125,785</t>
+          <t>124,407</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>592,393</t>
+          <t>588,678</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>122,631</t>
+          <t>121,489</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>347,289</t>
+          <t>344,859</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2.387,379</t>
+          <t>2.369,834</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>556,112</t>
+          <t>551,459</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>15.558,982</t>
+          <t>15.431,671</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>50000.0</t>
+          <t>200000.0</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>1.390,430</t>
+          <t>1.384,208</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>165,211</t>
+          <t>163,886</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6.060,253</t>
+          <t>5.941,253</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>2.185,880</t>
+          <t>2.168,505</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>63,837</t>
+          <t>63,321</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>838,049</t>
+          <t>830,131</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>15.819,078</t>
+          <t>15.719,475</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>5000.0</t>
+          <t>50000.0</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>9.472,413</t>
+          <t>9.412,983</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>100000.0</t>
+          <t>200000.0</t>
         </is>
       </c>
       <c r="Q51" s="4" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>21.145,854</t>
+          <t>20.988,542</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>50000.0</t>
+          <t>300000.0</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>13.384,828</t>
+          <t>13.310,330</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>100000.0</t>
+          <t>1000000.0</t>
         </is>
       </c>
       <c r="Q53" s="4" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>247,206</t>
+          <t>245,506</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6940,71 +6940,19 @@
           <t>https://www.caixa.gov.br/fundos-investimento/curto-prazo/fic-automatico-polis-rf-cp/Paginas/default.aspx</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>39.594.941/0001-36</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>6520</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>Conservador</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>D+0 (du)</t>
-        </is>
-      </c>
-      <c r="R54" s="2" t="inlineStr">
-        <is>
-          <t>D+00 (du)</t>
-        </is>
-      </c>
-      <c r="S54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6520.pdf</t>
-        </is>
-      </c>
-      <c r="T54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6520.pdf</t>
-        </is>
-      </c>
-      <c r="U54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6520.pdf</t>
-        </is>
-      </c>
-      <c r="V54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6520.pdf</t>
-        </is>
-      </c>
-      <c r="W54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6520.pdf</t>
-        </is>
-      </c>
-      <c r="X54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6520.pdf</t>
-        </is>
-      </c>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr"/>
+      <c r="W54" s="2" t="inlineStr"/>
+      <c r="X54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -7024,32 +6972,32 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,40949900</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>0,000</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>1,33</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>5,27</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>14,31</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>67,622</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
@@ -7146,32 +7094,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1.193,19101100</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>-0,002</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>3,81</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>-4,90</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>-0,75</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>36,431</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -7293,7 +7241,7 @@
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>327,947</t>
+          <t>540,035</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
@@ -7338,32 +7286,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1.637,20394000</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>-0,114</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>0,08</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>4,48</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>13,07</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>114,507</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -7485,7 +7433,7 @@
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>12,847</t>
+          <t>12,674</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
@@ -7700,32 +7648,32 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,25386200</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>-0,005</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>-0,15</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>2,66</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>10,74</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6,430</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
@@ -8062,32 +8010,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,42327300</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>-0,004</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>-3,09</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>4,26</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>17,44</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>11,840</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -8327,7 +8275,7 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>3,754</t>
+          <t>3,753</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -8424,32 +8372,32 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>5,33686931</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>-0,114</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>0,09</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>4,01</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>12,82</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32,833</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
@@ -8571,7 +8519,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>639,783</t>
+          <t>628,367</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8668,32 +8616,32 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>2,86271200</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>-0,004</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>0,34</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>2,49</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>10,66</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>74,533</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
@@ -8815,7 +8763,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>29,006</t>
+          <t>28,806</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8937,7 +8885,7 @@
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>2.402,829</t>
+          <t>2.388,736</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
@@ -9059,7 +9007,7 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>21,994</t>
+          <t>21,850</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -9156,32 +9104,32 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G73" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1.658,37370000</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>-0,110</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>0,16</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>4,86</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>14,05</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14,674</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
@@ -9274,32 +9222,32 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>0,52057047</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>-0,007</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>-4,04</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>-27,90</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,00</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3,876</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -9396,32 +9344,32 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>3,27988400</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>0,532</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>1,93</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>2,94</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>8,54</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>156,216</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
@@ -9518,32 +9466,32 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,54915500</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>0,003</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>1,01</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>3,75</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>20,28</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14,594</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -9640,32 +9588,32 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,37383500</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>-0,660</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>-1,70</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>1,30</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>7,37</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>70,402</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
@@ -9762,32 +9710,32 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,50209900</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>0,180</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>3,57</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>3,86</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>16,32</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>194,763</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9797,7 +9745,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/fic-capital-protegido-ciclico-ii-multimercado-lp/Paginas/default.aspx</t>
+          <t>https://www.caixa.gov.br/fundos-investimento/multimercado/caixa-fic-fim-cap-protegido-ciclico-ii</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -9884,32 +9832,32 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,77828200</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>-0,002</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>1,07</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>0,66</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>10,09</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>176,122</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -10031,7 +9979,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>902,819</t>
+          <t>898,155</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -10153,7 +10101,7 @@
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>747,266</t>
+          <t>745,586</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
@@ -10250,32 +10198,32 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>6,82921600</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>-0,004</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>0,75</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>6,18</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>16,85</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>128,939</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -10372,32 +10320,32 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,42390900</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>-0,003</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>1,09</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>3,35</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>16,21</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>281,056</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
@@ -10494,32 +10442,32 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,32775300</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>-0,002</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>1,41</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>3,44</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>3,06</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13,382</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -10641,7 +10589,7 @@
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>96,762</t>
+          <t>96,616</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
@@ -10763,7 +10711,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>340,588</t>
+          <t>340,536</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -11007,7 +10955,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>10,300</t>
+          <t>10,297</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -11125,7 +11073,7 @@
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>283,484</t>
+          <t>283,357</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
@@ -11247,7 +11195,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>446,677</t>
+          <t>446,580</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -11491,7 +11439,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>2,130</t>
+          <t>2,126</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -11613,7 +11561,7 @@
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>76,584</t>
+          <t>76,536</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -11735,7 +11683,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>90,397</t>
+          <t>90,378</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -11832,32 +11780,32 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G95" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H95" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1,27967300</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>-0,045</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>-6,28</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>-0,57</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>7,69</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>289,458</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -11979,7 +11927,7 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>114,891</t>
+          <t>114,886</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -12101,7 +12049,7 @@
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>127,209</t>
+          <t>127,196</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
@@ -12223,7 +12171,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>48,093</t>
+          <t>48,074</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -12345,7 +12293,7 @@
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>119,528</t>
+          <t>119,373</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
@@ -12467,7 +12415,7 @@
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>40,929</t>
+          <t>40,893</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -12589,7 +12537,7 @@
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>668,903</t>
+          <t>668,752</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
@@ -12711,7 +12659,7 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>446,282</t>
+          <t>446,175</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -13321,7 +13269,7 @@
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>35,566</t>
+          <t>35,541</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
@@ -13443,7 +13391,7 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>835,509</t>
+          <t>834,938</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -13565,7 +13513,7 @@
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>2,908</t>
+          <t>2,906</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
@@ -13809,7 +13757,7 @@
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>19,715</t>
+          <t>19,698</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
@@ -13931,7 +13879,7 @@
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>274,449</t>
+          <t>274,269</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
@@ -14028,32 +13976,32 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G113" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H113" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1.003,15033500</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>-0,003</t>
+        </is>
+      </c>
+      <c r="F113" s="7" t="inlineStr">
+        <is>
+          <t>-6,24</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>2,32</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>16,31</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7,913</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
@@ -14150,32 +14098,32 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1.505,83720300</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>-0,002</t>
+        </is>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
+        <is>
+          <t>-6,39</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>0,67</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>10,99</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21,900</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -14272,7 +14220,7 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>169,55922300</t>
+          <t>169,55922343</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
@@ -14541,7 +14489,7 @@
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>1.616,184</t>
+          <t>1.615,388</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
@@ -14785,7 +14733,7 @@
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>785,583</t>
+          <t>785,107</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
@@ -14795,17 +14743,17 @@
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-vale-do-rio-doce-1</t>
+          <t>http://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-vale-do-rio-doce-2</t>
         </is>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>04.885.818/0001-90</t>
+          <t>04.885.824/0001-47</t>
         </is>
       </c>
       <c r="M119" s="4" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="N119" s="4" t="inlineStr">
@@ -14815,12 +14763,12 @@
       </c>
       <c r="O119" s="4" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="Q119" s="4" t="inlineStr">
@@ -14835,32 +14783,32 @@
       </c>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5206.pdf</t>
         </is>
       </c>
       <c r="T119" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5205.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5206.pdf</t>
         </is>
       </c>
       <c r="U119" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5206.pdf</t>
         </is>
       </c>
       <c r="V119" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5206.pdf</t>
         </is>
       </c>
       <c r="W119" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5206.pdf</t>
         </is>
       </c>
       <c r="X119" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5206.pdf</t>
         </is>
       </c>
     </row>
@@ -14907,7 +14855,7 @@
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>113,591</t>
+          <t>113,569</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
@@ -15151,7 +15099,7 @@
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>582,688</t>
+          <t>581,978</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
@@ -15273,7 +15221,7 @@
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>470,938</t>
+          <t>470,848</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
@@ -15283,17 +15231,17 @@
       </c>
       <c r="K123" s="4" t="inlineStr">
         <is>
-          <t>http://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-vale-do-rio-doce-1</t>
+          <t>http://www.caixa.gov.br/fundos-investimento/mutuos-privatizacao/fmp-fgts-vale-do-rio-doce-2</t>
         </is>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
-          <t>04.885.818/0001-90</t>
+          <t>04.885.824/0001-47</t>
         </is>
       </c>
       <c r="M123" s="4" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="N123" s="4" t="inlineStr">
@@ -15303,12 +15251,12 @@
       </c>
       <c r="O123" s="4" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10000.0</t>
         </is>
       </c>
       <c r="Q123" s="4" t="inlineStr">
@@ -15323,32 +15271,32 @@
       </c>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5206.pdf</t>
         </is>
       </c>
       <c r="T123" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5205.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5206.pdf</t>
         </is>
       </c>
       <c r="U123" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5206.pdf</t>
         </is>
       </c>
       <c r="V123" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_5206.pdf</t>
         </is>
       </c>
       <c r="W123" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5206.pdf</t>
         </is>
       </c>
       <c r="X123" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5205.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5206.pdf</t>
         </is>
       </c>
     </row>
@@ -15395,7 +15343,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>670,495</t>
+          <t>669,850</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -15639,7 +15587,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>215,263</t>
+          <t>196,696</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -15761,7 +15709,7 @@
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>41,338</t>
+          <t>41,030</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
@@ -15883,7 +15831,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>791,217</t>
+          <t>784,325</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -16005,7 +15953,7 @@
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>18,924</t>
+          <t>18,812</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
@@ -16127,7 +16075,7 @@
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>94,973</t>
+          <t>94,369</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -16249,7 +16197,7 @@
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>7.939,338</t>
+          <t>7.710,838</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
@@ -16371,7 +16319,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>15.867,048</t>
+          <t>15.793,725</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -16406,7 +16354,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>1000000.0</t>
+          <t>3000000.0</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16493,7 +16441,7 @@
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>3.045,452</t>
+          <t>3.031,660</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
@@ -16528,7 +16476,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>1000000.0</t>
+          <t>3000000.0</t>
         </is>
       </c>
       <c r="Q133" s="4" t="inlineStr">
@@ -16590,7 +16538,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>1,54654300</t>
+          <t>1,54654296</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -16737,7 +16685,7 @@
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>285,149</t>
+          <t>284,379</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
@@ -16859,7 +16807,7 @@
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>4.013,008</t>
+          <t>4.011,477</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -16981,7 +16929,7 @@
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>4.781,473</t>
+          <t>4.780,987</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
@@ -17099,7 +17047,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>13.989,956</t>
+          <t>13.597,824</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -17221,7 +17169,7 @@
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>12.515,793</t>
+          <t>12.463,903</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
@@ -17256,7 +17204,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>1000000.0</t>
+          <t>3000000.0</t>
         </is>
       </c>
       <c r="Q139" s="4" t="inlineStr">
@@ -17343,7 +17291,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>3.596,587</t>
+          <t>3.582,717</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
@@ -17378,7 +17326,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>1000000.0</t>
+          <t>3000000.0</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17465,7 +17413,7 @@
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>1.468,990</t>
+          <t>1.461,203</t>
         </is>
       </c>
       <c r="J141" s="4" t="inlineStr">
@@ -17587,7 +17535,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>33.690,972</t>
+          <t>31.773,754</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -17709,7 +17657,7 @@
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>3.007,512</t>
+          <t>2.804,769</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
@@ -17831,7 +17779,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>16.519,133</t>
+          <t>16.634,401</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -18456,12 +18404,12 @@
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
-          <t>14.508.605/0001-00</t>
+          <t>10.740.670/0001-06</t>
         </is>
       </c>
       <c r="M149" s="4" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="N149" s="4" t="inlineStr">
@@ -18491,32 +18439,32 @@
       </c>
       <c r="S149" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5824.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5464.pdf</t>
         </is>
       </c>
       <c r="T149" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5824.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5464.pdf</t>
         </is>
       </c>
       <c r="U149" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5464.pdf</t>
         </is>
       </c>
       <c r="V149" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5464.pdf</t>
         </is>
       </c>
       <c r="W149" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5464.pdf</t>
         </is>
       </c>
       <c r="X149" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5464.pdf</t>
         </is>
       </c>
     </row>
@@ -18700,12 +18648,12 @@
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
-          <t>14.508.605/0001-00</t>
+          <t>10.740.670/0001-06</t>
         </is>
       </c>
       <c r="M151" s="4" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="N151" s="4" t="inlineStr">
@@ -18735,32 +18683,32 @@
       </c>
       <c r="S151" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5824.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5464.pdf</t>
         </is>
       </c>
       <c r="T151" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5824.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5464.pdf</t>
         </is>
       </c>
       <c r="U151" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5464.pdf</t>
         </is>
       </c>
       <c r="V151" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5464.pdf</t>
         </is>
       </c>
       <c r="W151" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5464.pdf</t>
         </is>
       </c>
       <c r="X151" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5464.pdf</t>
         </is>
       </c>
     </row>
@@ -19365,7 +19313,7 @@
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>720,376</t>
+          <t>720,375</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
@@ -19380,12 +19328,12 @@
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
-          <t>14.508.605/0001-00</t>
+          <t>10.740.670/0001-06</t>
         </is>
       </c>
       <c r="M157" s="4" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="N157" s="4" t="inlineStr">
@@ -19415,32 +19363,32 @@
       </c>
       <c r="S157" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5824.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5464.pdf</t>
         </is>
       </c>
       <c r="T157" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5824.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5464.pdf</t>
         </is>
       </c>
       <c r="U157" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5464.pdf</t>
         </is>
       </c>
       <c r="V157" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5464.pdf</t>
         </is>
       </c>
       <c r="W157" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5464.pdf</t>
         </is>
       </c>
       <c r="X157" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5824.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5464.pdf</t>
         </is>
       </c>
     </row>
@@ -19487,7 +19435,7 @@
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>12.901,464</t>
+          <t>12.901,293</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
@@ -19502,12 +19450,12 @@
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>03.737.206/0001-97</t>
+          <t>05.164.356/0001-84</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -19537,32 +19485,32 @@
       </c>
       <c r="S158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5404.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5462.pdf</t>
         </is>
       </c>
       <c r="T158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5404.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5462.pdf</t>
         </is>
       </c>
       <c r="U158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5404.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5462.pdf</t>
         </is>
       </c>
       <c r="V158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5404.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5462.pdf</t>
         </is>
       </c>
       <c r="W158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5404.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5462.pdf</t>
         </is>
       </c>
       <c r="X158" s="2" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5404.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5462.pdf</t>
         </is>
       </c>
     </row>
@@ -19609,7 +19557,7 @@
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>4.621,489</t>
+          <t>4.621,477</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
@@ -19853,7 +19801,7 @@
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>1.750,478</t>
+          <t>1.543,199</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
@@ -19975,7 +19923,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>23.815,568</t>
+          <t>23.815,493</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
@@ -20289,7 +20237,7 @@
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>295,252</t>
+          <t>295,234</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
@@ -20508,7 +20456,7 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>11,49497800</t>
+          <t>11,49497823</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -20874,7 +20822,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>3,41371100</t>
+          <t>3,41371062</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
@@ -20992,7 +20940,7 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>2,48907700</t>
+          <t>2,48907659</t>
         </is>
       </c>
       <c r="E171" s="7" t="inlineStr">
@@ -21135,7 +21083,7 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>4.929,702</t>
+          <t>4.880,670</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
